--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:56</t>
+          <t>2026-09-03 00:54:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:57</t>
+          <t>2026-09-03 00:54:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:34:59</t>
+          <t>2026-09-03 00:54:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:00</t>
+          <t>2026-09-03 00:54:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:09</t>
+          <t>2026-09-03 01:13:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:09</t>
+          <t>2026-09-03 01:13:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:09</t>
+          <t>2026-09-03 01:13:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:09</t>
+          <t>2026-09-03 01:13:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:10</t>
+          <t>2026-09-03 01:13:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:10</t>
+          <t>2026-09-03 01:13:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:10</t>
+          <t>2026-09-03 01:13:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:10</t>
+          <t>2026-09-03 01:13:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:10</t>
+          <t>2026-09-03 01:13:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:12</t>
+          <t>2026-09-03 01:13:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:13</t>
+          <t>2026-09-03 01:13:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:46</t>
+          <t>2026-09-03 21:58:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:46</t>
+          <t>2026-09-03 21:58:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>923</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:46</t>
+          <t>2026-09-03 21:58:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:46</t>
+          <t>2026-09-03 21:58:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:47</t>
+          <t>2026-09-03 21:58:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:47</t>
+          <t>2026-09-03 21:58:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:47</t>
+          <t>2026-09-03 21:58:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:47</t>
+          <t>2026-09-03 21:58:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:47</t>
+          <t>2026-09-03 21:58:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>-3.51%261</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>270.5</t>
+          <t>261</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:49</t>
+          <t>2026-09-03 21:58:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:50</t>
+          <t>2026-09-03 21:58:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:13</t>
+          <t>2026-09-03 22:32:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:13</t>
+          <t>2026-09-03 22:32:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:13</t>
+          <t>2026-09-03 22:32:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:13</t>
+          <t>2026-09-03 22:32:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:25</t>
+          <t>2026-09-03 22:32:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:25</t>
+          <t>2026-09-03 22:32:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:25</t>
+          <t>2026-09-03 22:32:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:25</t>
+          <t>2026-09-03 22:32:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:25</t>
+          <t>2026-09-03 22:32:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:36</t>
+          <t>2026-09-03 22:32:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:47</t>
+          <t>2026-09-03 22:32:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:43</t>
+          <t>2026-09-03 22:45:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:43</t>
+          <t>2026-09-03 22:45:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:43</t>
+          <t>2026-09-03 22:45:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:43</t>
+          <t>2026-09-03 22:45:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:44</t>
+          <t>2026-09-03 22:45:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:44</t>
+          <t>2026-09-03 22:45:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:44</t>
+          <t>2026-09-03 22:45:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:44</t>
+          <t>2026-09-03 22:45:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:44</t>
+          <t>2026-09-03 22:45:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:45</t>
+          <t>2026-09-03 22:45:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:46</t>
+          <t>2026-09-03 22:45:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:08</t>
+          <t>2026-09-03 23:01:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:10</t>
+          <t>2026-09-03 23:01:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:11</t>
+          <t>2026-09-03 23:01:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:12</t>
+          <t>2026-09-03 23:01:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
